--- a/excel/50000(n)/AVG_Sort_Dataset.xlsx
+++ b/excel/50000(n)/AVG_Sort_Dataset.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#Java-Practice\##SS2\Lab3 Sorting\excel\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>InputSize(n)</t>
   </si>
@@ -43,12 +43,28 @@
   </si>
   <si>
     <t xml:space="preserve">BubbleSort </t>
+  </si>
+  <si>
+    <t>BubbleSort (Reverse)</t>
+  </si>
+  <si>
+    <t>InsertionSort (Reverse)</t>
+  </si>
+  <si>
+    <t>SelectionSort (Reverse)</t>
+  </si>
+  <si>
+    <t>MergeSort (Reverse)</t>
+  </si>
+  <si>
+    <t>QuickSort (Reverse)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -360,35 +376,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="21.33203125"/>
+    <col min="2" max="2" customWidth="true" width="15.77734375"/>
+    <col min="3" max="3" customWidth="true" width="15.44140625"/>
+    <col min="4" max="4" customWidth="true" width="13.5546875"/>
+    <col min="5" max="5" customWidth="true" width="14.88671875"/>
+    <col min="6" max="6" customWidth="true" width="12.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>4</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>50000.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>2.721107052E9</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.21704544E8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.49726428E8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9540624.0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8465780.0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.703405192E9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.22625472E8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.52460984E8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7460164.0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.33836E7</v>
       </c>
     </row>
   </sheetData>
